--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T19:11:07+00:00</t>
+    <t>2026-01-16T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:21:16+00:00</t>
+    <t>2026-01-19T10:22:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation geplante Abgabe</t>
+    <t>ELGA e-Medikation Geplante Abgabe</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:22:08+00:00</t>
+    <t>2026-01-20T10:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,9 +87,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:**Bildet eine geplante Abgabe eines Arzneimittels aus dem entsprechendem Medikationsplaneintrag des ELGA Teilnehmers ab (Rezeptierung). Sie enthält das verordnetes Arzneimittel und dessen Dosierung, der Status ist bei Ausstellung aktiv. 
-Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird.
-Werden mehrere Arzneimittel gleichzeitig verordnet, so wird für jedes Arzneimittel eine eigene geplante Abgabe erstellt, der groupIdentifier ist aber für diese geplanten Abgaben gleich (Bildet 'Rezept-Klammer').</t>
+    <t>**Beschreibung:** Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab.
+Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. 
+Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
+Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
+Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -268,14 +273,14 @@
 </t>
   </si>
   <si>
-    <t>Ordering of medication for patient or group</t>
+    <t>Geplante Abgabe eines Arzneimittels aus dem Medikationsplan.</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}med-1:Für die geplante Abgabe muss entweder CodeableConcept (PZN) oder Reference(Medication) angegeben werden – aber genau eins. {medicationCodeableConcept.exists() xor medicationReference.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -481,7 +486,7 @@
 </t>
   </si>
   <si>
-    <t>External ids for this request</t>
+    <t>Geplante-Abgabe-ID (früher eMed-ID), bildet 'Rezept-Klammer' bei mehreren gleichzeitig ausgestellten geplanten Abgaben.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -508,7 +513,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>active | aktiv</t>
+    <t>Status der geplanten Abgabe (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -545,7 +550,7 @@
 </t>
   </si>
   <si>
-    <t>Reason for current status</t>
+    <t>Grund für den aktuellen Status: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -572,7 +577,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>Die Geplante Abgabe stellt eine Anforderung und Ermächtigung zum Handeln durch den Antragsteller dar, daher ist intent immer "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -585,6 +590,9 @@
 This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
   </si>
   <si>
+    <t>order</t>
+  </si>
+  <si>
     <t>The kind of medication order.</t>
   </si>
   <si>
@@ -603,7 +611,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Type of medication usage</t>
+    <t>Art der Medikamentenanforderung (z.B. ambulante oder stationäre Einnahme oder Verabreichung)</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -631,7 +639,7 @@
     <t>MedicationRequest.priority</t>
   </si>
   <si>
-    <t>routine | urgent | asap | stat</t>
+    <t>Priorität der geplanten Abgabe: routine | urgent | asap | stat. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
@@ -659,7 +667,7 @@
 </t>
   </si>
   <si>
-    <t>True if request is prohibiting action</t>
+    <t>Gibt an, ob die geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -678,7 +686,7 @@
 Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
-    <t>Reported rather than primary record</t>
+    <t>Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
@@ -691,7 +699,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|4.0.1)</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
   </si>
   <si>
     <t>Medication to be taken</t>
@@ -707,6 +715,13 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -730,14 +745,279 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept</t>
+  </si>
+  <si>
+    <t>medicationCodeableConcept</t>
+  </si>
+  <si>
+    <t>Angabe mittels Pharmazentralnummer (PZN) aus der ASP-Liste.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/asp-liste</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference</t>
+  </si>
+  <si>
+    <t>medicationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
+  </si>
+  <si>
+    <t>Bei magistralen Anwendungen oder Infusionen ohne PZN.</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
-    <t>Who or group medication request is for</t>
+    <t>Österreichischer Patient für den die geplante Abgabe ausgestellt wird.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -770,9 +1050,6 @@
 </t>
   </si>
   <si>
-    <t>Encounter created as part of encounter/admission/stay</t>
-  </si>
-  <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
   </si>
   <si>
@@ -798,9 +1075,6 @@
 </t>
   </si>
   <si>
-    <t>Information to support ordering of the medication</t>
-  </si>
-  <si>
     <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
   </si>
   <si>
@@ -817,7 +1091,7 @@
 </t>
   </si>
   <si>
-    <t>When request was initially authored</t>
+    <t>Datum der Ausstellung der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -841,11 +1115,11 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
-    <t>Who/What requested the Request</t>
+    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -864,9 +1138,6 @@
 </t>
   </si>
   <si>
-    <t>Intended performer of administration</t>
-  </si>
-  <si>
     <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
   </si>
   <si>
@@ -880,9 +1151,6 @@
   </si>
   <si>
     <t>MedicationRequest.performerType</t>
-  </si>
-  <si>
-    <t>Desired kind of performer of the medication administration</t>
   </si>
   <si>
     <t>Indicates the type of performer of the administration of the medication.</t>
@@ -910,9 +1178,6 @@
 </t>
   </si>
   <si>
-    <t>Person who entered the request</t>
-  </si>
-  <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
   </si>
   <si>
@@ -925,7 +1190,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Reason or indication for ordering or not ordering the medication</t>
+    <t>Grund für die Verordnung des Arzneimittels. Annahme: Keine Verwendung in der geplanten Abgabe, reasonReference ausreichend.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -962,7 +1227,7 @@
 </t>
   </si>
   <si>
-    <t>Condition or observation that supports why the prescription is being written</t>
+    <t>Grund für die Verordnung des Arzneimittels (Referenz). Verwendung erst, wenn e-Diagnose referenzierbar ist.</t>
   </si>
   <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
@@ -984,9 +1249,6 @@
 </t>
   </si>
   <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
   </si>
   <si>
@@ -999,20 +1261,17 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
   </si>
   <si>
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|MedicationRequest|4.0.1|ServiceRequest|4.0.1|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medicationrequest-planeintrag)
 </t>
   </si>
   <si>
-    <t>What request fulfills</t>
+    <t>Referenz auf den zugrundeliegenden Medikationsplaneintrag, auf dem diese geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1027,7 +1286,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Composite request this is part of</t>
+    <t>Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird. Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1045,7 +1304,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Overall pattern of medication administration</t>
+    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Evtl. im Planeintrag (dosageInstruction), paused soll im Status dokumentiert werden.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -1070,7 +1329,7 @@
 </t>
   </si>
   <si>
-    <t>Associated insurance coverage</t>
+    <t>Zusätzliche Informationen zur geplanten Abgabe, die durch die anderen Attribute nicht abgebildet werden konnten. Dzt. unklar, ob erforderlich.</t>
   </si>
   <si>
     <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be required for delivering the requested service.</t>
@@ -1111,7 +1370,7 @@
 </t>
   </si>
   <si>
-    <t>How the medication should be taken</t>
+    <t>Anweisungen zur Einnahme/Verabreichung des Arzneimittels.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1148,29 +1407,7 @@
     <t>MedicationRequest.dispenseRequest.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -1440,7 +1677,7 @@
 </t>
   </si>
   <si>
-    <t>An order/prescription that is being replaced</t>
+    <t>Im Falle einer Änderung wird auf die ersetzte Verordnungen/MedicationRequests verwiesen.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -1623,6 +1860,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1804,12 +2056,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="67.0546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1817,7 +2069,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="205.50390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1835,7 +2087,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1974,7 +2226,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2089,7 +2341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2206,7 +2458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2321,7 +2573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2438,7 +2690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2555,7 +2807,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2672,7 +2924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2789,7 +3041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2906,7 +3158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3038,13 +3290,13 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -3142,7 +3394,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -3259,7 +3511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -3275,7 +3527,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3395,7 +3647,7 @@
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>91</v>
@@ -3424,7 +3676,7 @@
         <v>21</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>21</v>
@@ -3442,10 +3694,10 @@
         <v>161</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3478,27 +3730,27 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3509,7 +3761,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -3524,13 +3776,13 @@
         <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3559,10 +3811,10 @@
         <v>173</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3580,7 +3832,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3598,24 +3850,24 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3626,7 +3878,7 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3641,10 +3893,10 @@
         <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3674,10 +3926,10 @@
         <v>161</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3695,7 +3947,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3710,27 +3962,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3741,7 +3993,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3753,16 +4005,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3812,7 +4064,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3833,7 +4085,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -3842,12 +4094,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3858,7 +4110,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3870,13 +4122,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3927,7 +4179,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3948,7 +4200,7 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3957,12 +4209,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3976,7 +4228,7 @@
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -3985,16 +4237,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4023,28 +4275,26 @@
         <v>173</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4059,41 +4309,43 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
@@ -4102,16 +4354,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4137,13 +4389,11 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4161,7 +4411,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4176,27 +4426,27 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4219,17 +4469,15 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4278,7 +4526,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4290,34 +4538,34 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4336,15 +4584,17 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>246</v>
+        <v>136</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>137</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4381,19 +4631,19 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4405,30 +4655,30 @@
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4436,7 +4686,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4451,16 +4701,20 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4508,13 +4762,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4523,27 +4777,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM23" t="s" s="2">
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="B24" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4563,16 +4817,16 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4623,7 +4877,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4635,41 +4889,41 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4681,15 +4935,17 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4726,54 +4982,54 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4781,7 +5037,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -4796,18 +5052,20 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4831,13 +5089,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4855,7 +5113,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4870,27 +5128,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4910,18 +5168,20 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4970,7 +5230,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4991,21 +5251,21 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5013,10 +5273,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -5025,21 +5285,21 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5063,13 +5323,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5087,13 +5347,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -5102,27 +5362,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5130,33 +5390,33 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5204,13 +5464,13 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -5219,27 +5479,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5250,7 +5510,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5262,16 +5522,20 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5319,13 +5583,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5334,27 +5598,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5365,7 +5629,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5377,16 +5641,20 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>235</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5434,13 +5702,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5461,17 +5729,19 @@
         <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5480,10 +5750,10 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5492,15 +5762,17 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5549,13 +5821,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5564,27 +5836,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>318</v>
+        <v>224</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>319</v>
+        <v>226</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5592,13 +5864,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5607,18 +5879,18 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5666,10 +5938,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5681,22 +5953,22 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AN33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>326</v>
       </c>
@@ -5712,7 +5984,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5724,10 +5996,10 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>328</v>
@@ -5759,13 +6031,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5798,27 +6070,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN34" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO34" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5829,7 +6101,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -5841,10 +6113,10 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>212</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>336</v>
@@ -5898,7 +6170,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5922,7 +6194,7 @@
         <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -5941,19 +6213,19 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>340</v>
@@ -6019,7 +6291,7 @@
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6037,18 +6309,18 @@
         <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6056,32 +6328,30 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6130,13 +6400,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6145,27 +6415,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6176,7 +6446,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6188,10 +6458,10 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>212</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>356</v>
@@ -6245,7 +6515,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6260,27 +6530,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>358</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6291,7 +6561,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6300,18 +6570,20 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>360</v>
+        <v>169</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6336,13 +6608,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6360,7 +6632,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6372,16 +6644,16 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6390,23 +6662,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6418,17 +6690,15 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6483,13 +6753,13 @@
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6498,25 +6768,25 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6529,26 +6799,24 @@
         <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6572,13 +6840,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6608,30 +6876,30 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>133</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6642,10 +6910,10 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6654,16 +6922,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6713,13 +6981,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6728,27 +6996,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6759,7 +7027,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6768,16 +7036,16 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>212</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6828,28 +7096,28 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6858,23 +7126,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6883,20 +7151,18 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6945,7 +7211,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6957,7 +7223,7 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -6966,7 +7232,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -6975,48 +7241,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>398</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7064,7 +7326,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7076,16 +7338,16 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>133</v>
+        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7094,12 +7356,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7119,19 +7381,21 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>382</v>
+        <v>148</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7179,7 +7443,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7194,13 +7458,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7209,12 +7473,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7225,7 +7489,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7237,15 +7501,17 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7270,13 +7536,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>414</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7294,7 +7560,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7315,7 +7581,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7324,12 +7590,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7340,7 +7606,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7352,13 +7618,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7409,13 +7675,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7424,13 +7690,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7439,12 +7705,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7455,7 +7721,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7467,20 +7733,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7528,13 +7790,13 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
@@ -7543,13 +7805,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7558,12 +7820,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7574,7 +7836,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7586,16 +7848,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7645,13 +7907,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7660,27 +7922,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7703,13 +7965,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>437</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7760,7 +8022,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7778,24 +8040,24 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>415</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7818,17 +8080,15 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>387</v>
+        <v>235</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>236</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7877,7 +8137,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>238</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7889,16 +8149,16 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>421</v>
+        <v>239</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7907,23 +8167,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7935,15 +8195,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>423</v>
+        <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>424</v>
+        <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7992,19 +8254,19 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>422</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8013,53 +8275,57 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>426</v>
+        <v>239</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>354</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8107,28 +8373,28 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>431</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8137,12 +8403,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8165,15 +8431,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>360</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>361</v>
+        <v>450</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8222,7 +8490,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8234,7 +8502,7 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -8243,7 +8511,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8252,23 +8520,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8280,17 +8548,15 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8339,19 +8605,19 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>238</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8360,7 +8626,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>364</v>
+        <v>239</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8369,16 +8635,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8391,26 +8657,24 @@
         <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>370</v>
+        <v>137</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
+        <v>242</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8458,7 +8722,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>246</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8479,7 +8743,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8488,46 +8752,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>436</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8551,13 +8817,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -8575,42 +8841,42 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>442</v>
+        <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8633,13 +8899,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>169</v>
+        <v>458</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8666,13 +8932,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -8690,7 +8956,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8708,24 +8974,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>451</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8748,13 +9014,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8805,7 +9071,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8820,13 +9086,13 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>456</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8835,23 +9101,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8863,17 +9129,15 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8922,13 +9186,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -8943,7 +9207,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8952,12 +9216,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8968,7 +9232,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8980,18 +9244,20 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9039,13 +9305,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9054,22 +9320,1551 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO75">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI74">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="547">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:13:19+00:00</t>
+    <t>2026-01-21T17:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,7 +486,7 @@
 </t>
   </si>
   <si>
-    <t>Geplante-Abgabe-ID (früher eMed-ID), bildet 'Rezept-Klammer' bei mehreren gleichzeitig ausgestellten geplanten Abgaben.</t>
+    <t>MedicationRequest identifier = {eMed-ID}_{locally assigned ID}  Setzt sich zusammen aus groupIdentifier (Rezept-Klammer) und individueller Identifikation der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -611,7 +611,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Art der Medikamentenanforderung (z.B. ambulante oder stationäre Einnahme oder Verabreichung)</t>
+    <t>Kategorie damit geplante Abgabe von Medikationsplaneintrag unterschieden werden kann</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -1190,7 +1190,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels. Annahme: Keine Verwendung in der geplanten Abgabe, reasonReference ausreichend.</t>
+    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz (evtl. Invariante).</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1225,9 +1225,6 @@
   <si>
     <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1)
 </t>
-  </si>
-  <si>
-    <t>Grund für die Verordnung des Arzneimittels (Referenz). Verwendung erst, wenn e-Diagnose referenzierbar ist.</t>
   </si>
   <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
@@ -3761,7 +3758,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -4689,7 +4686,7 @@
         <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -5377,7 +5374,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>286</v>
       </c>
@@ -5396,7 +5393,7 @@
         <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -6925,13 +6922,13 @@
         <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6996,13 +6993,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>165</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>381</v>
@@ -7013,10 +7010,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7039,13 +7036,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>212</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7096,7 +7093,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7111,13 +7108,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7128,10 +7125,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7160,7 +7157,7 @@
         <v>212</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7211,7 +7208,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7232,7 +7229,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7243,10 +7240,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7269,13 +7266,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7326,7 +7323,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7341,27 +7338,27 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7369,13 +7366,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7387,14 +7384,14 @@
         <v>148</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7443,7 +7440,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7458,13 +7455,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7475,10 +7472,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7504,13 +7501,13 @@
         <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7539,11 +7536,11 @@
         <v>173</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7560,7 +7557,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7581,7 +7578,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7592,10 +7589,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7618,13 +7615,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7675,7 +7672,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7690,13 +7687,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7707,10 +7704,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7733,13 +7730,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7790,7 +7787,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7805,13 +7802,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7822,10 +7819,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7848,16 +7845,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7907,7 +7904,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7922,13 +7919,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7939,10 +7936,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7965,13 +7962,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8022,7 +8019,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8040,10 +8037,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8054,10 +8051,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8169,10 +8166,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8286,14 +8283,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8315,10 +8312,10 @@
         <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8373,7 +8370,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8405,10 +8402,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8431,16 +8428,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8490,7 +8487,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8511,7 +8508,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8522,10 +8519,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8637,10 +8634,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8754,14 +8751,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8783,10 +8780,10 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>139</v>
@@ -8841,7 +8838,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8873,10 +8870,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8899,13 +8896,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8956,7 +8953,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8977,7 +8974,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8988,10 +8985,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9014,13 +9011,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9071,7 +9068,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9092,7 +9089,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9103,10 +9100,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9129,13 +9126,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9186,7 +9183,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9207,7 +9204,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9218,10 +9215,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9244,19 +9241,19 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9305,7 +9302,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9323,10 +9320,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9337,10 +9334,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9363,16 +9360,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9422,7 +9419,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9440,24 +9437,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9480,13 +9477,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9537,7 +9534,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9555,24 +9552,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9595,16 +9592,16 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9654,7 +9651,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9672,10 +9669,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9686,10 +9683,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9712,13 +9709,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9769,7 +9766,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9790,7 +9787,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>371</v>
@@ -9801,10 +9798,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9827,13 +9824,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9884,7 +9881,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9902,10 +9899,10 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9916,10 +9913,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10031,10 +10028,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10148,14 +10145,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10177,10 +10174,10 @@
         <v>136</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>139</v>
@@ -10235,7 +10232,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10267,10 +10264,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10293,16 +10290,16 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10331,11 +10328,11 @@
         <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10352,7 +10349,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>90</v>
@@ -10370,24 +10367,24 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10413,10 +10410,10 @@
         <v>169</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10446,11 +10443,11 @@
         <v>173</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10467,7 +10464,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10485,24 +10482,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10525,13 +10522,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10582,7 +10579,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10597,13 +10594,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10614,14 +10611,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10640,16 +10637,16 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10699,7 +10696,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10720,7 +10717,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10731,10 +10728,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10757,16 +10754,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10816,7 +10813,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10831,13 +10828,13 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T17:03:29+00:00</t>
+    <t>2026-01-22T09:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T09:24:15+00:00</t>
+    <t>2026-01-22T12:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T12:59:21+00:00</t>
+    <t>2026-01-22T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-geplanteAbgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$134</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4573" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4982" uniqueCount="802">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T19:34:42+00:00</t>
+    <t>2026-01-26T15:48:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,10 +88,9 @@
   </si>
   <si>
     <t>**Beschreibung:** Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab.
-Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. 
-Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
+Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
 Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
-Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
+Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -273,7 +272,7 @@
 </t>
   </si>
   <si>
-    <t>Geplante Abgabe eines Arzneimittels aus dem Medikationsplan.</t>
+    <t>Geplante Abgabe eines Arzneimittels aus dem Medikationsplan. Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -513,7 +512,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
+    <t>Status der geplanten Abgabe (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -611,7 +610,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Kategorie damit geplante Abgabe von Medikationsplaneintrag unterschieden werden kann</t>
+    <t>Kategorie damit geplante Abgabe von Medikationsplaneintrag unterschieden werden kann.</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -1233,6 +1232,39 @@
   </si>
   <si>
     <t>ORC-16-Order Control Code Reason /RXE-27-Give Indication/RXO-20-Indication / RXD-21-Indication / RXG-22-Indication / RXA-19-Indication</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.text</t>
   </si>
   <si>
     <t>MedicationRequest.reasonReference</t>
@@ -2801,7 +2833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO123"/>
+  <dimension ref="A1:AO134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.0546875" customWidth="true" bestFit="true"/>
@@ -8107,7 +8139,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>387</v>
       </c>
@@ -8123,10 +8155,10 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -8135,17 +8167,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>388</v>
+        <v>196</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>197</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -8194,31 +8224,31 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>199</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>392</v>
+        <v>200</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -8226,21 +8256,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -8249,18 +8279,20 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>394</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -8297,19 +8329,19 @@
         <v>21</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8321,16 +8353,16 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>200</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -8341,10 +8373,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8352,10 +8384,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -8367,16 +8399,20 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>400</v>
+        <v>209</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -8424,7 +8460,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>399</v>
+        <v>214</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8445,21 +8481,21 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>398</v>
+        <v>215</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8467,7 +8503,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
@@ -8479,16 +8515,16 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>403</v>
+        <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>404</v>
+        <v>197</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>405</v>
+        <v>198</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8539,28 +8575,28 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>199</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>407</v>
+        <v>200</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -8569,46 +8605,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8644,40 +8680,40 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>408</v>
+        <v>206</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>413</v>
+        <v>200</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -8688,10 +8724,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8699,10 +8735,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8711,21 +8747,23 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>415</v>
+        <v>274</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>416</v>
+        <v>275</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8749,13 +8787,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8773,7 +8811,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>278</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8794,21 +8832,21 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>420</v>
+        <v>279</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8819,7 +8857,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8828,18 +8866,20 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>422</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8888,13 +8928,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>421</v>
+        <v>286</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8903,27 +8943,27 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>425</v>
+        <v>287</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8931,10 +8971,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8943,19 +8983,21 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>427</v>
+        <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>291</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
+        <v>292</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -9003,13 +9045,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -9018,27 +9060,27 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>432</v>
+        <v>295</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9046,10 +9088,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -9058,21 +9100,21 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>196</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>299</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -9120,13 +9162,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>302</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -9135,27 +9177,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>303</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9175,19 +9217,23 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>197</v>
+        <v>307</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -9235,7 +9281,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9247,7 +9293,7 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -9256,32 +9302,32 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>200</v>
+        <v>312</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -9290,21 +9336,23 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -9340,31 +9388,31 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -9373,25 +9421,25 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9401,29 +9449,27 @@
         <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>399</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -9471,7 +9517,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>398</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9483,19 +9529,19 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>133</v>
+        <v>403</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -9503,10 +9549,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>404</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
+        <v>404</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9517,7 +9563,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -9529,18 +9575,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>448</v>
+        <v>405</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>449</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>450</v>
+        <v>407</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9588,13 +9632,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>404</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9603,27 +9647,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9634,7 +9678,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9646,18 +9690,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9705,13 +9747,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -9726,21 +9768,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>413</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>461</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9748,10 +9790,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9763,20 +9805,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>169</v>
+        <v>414</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9800,13 +9838,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>467</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9824,7 +9862,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>468</v>
+        <v>413</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9839,27 +9877,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>453</v>
+        <v>418</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>469</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9867,13 +9905,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
@@ -9882,16 +9920,18 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9939,7 +9979,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>473</v>
+        <v>419</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9954,27 +9994,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>469</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9985,7 +10025,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9994,23 +10034,21 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>475</v>
+        <v>169</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>426</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>427</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -10034,13 +10072,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -10058,7 +10096,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10079,7 +10117,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -10090,10 +10128,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10104,7 +10142,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -10116,13 +10154,13 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>196</v>
+        <v>433</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>198</v>
+        <v>434</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10173,28 +10211,28 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>199</v>
+        <v>432</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>200</v>
+        <v>436</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -10205,14 +10243,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10231,17 +10269,15 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>136</v>
+        <v>438</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>137</v>
+        <v>439</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -10278,19 +10314,19 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>206</v>
+        <v>437</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10302,16 +10338,16 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>200</v>
+        <v>443</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -10322,14 +10358,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>444</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10342,26 +10378,24 @@
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>445</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10409,7 +10443,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10421,16 +10455,16 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>450</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -10441,10 +10475,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10455,7 +10489,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -10464,21 +10498,19 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>486</v>
+        <v>197</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>487</v>
+        <v>198</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>488</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -10526,19 +10558,19 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>489</v>
+        <v>199</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -10547,7 +10579,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>490</v>
+        <v>200</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10558,21 +10590,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -10581,21 +10613,21 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>492</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>137</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10631,31 +10663,31 @@
         <v>21</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>206</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>497</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -10664,7 +10696,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>498</v>
+        <v>200</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10675,42 +10707,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>453</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>197</v>
+        <v>455</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10758,19 +10794,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>199</v>
+        <v>457</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -10779,7 +10815,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10790,21 +10826,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>500</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>500</v>
+        <v>458</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10813,21 +10849,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>137</v>
+        <v>460</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10863,31 +10899,31 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>206</v>
+        <v>463</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10896,21 +10932,21 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>200</v>
+        <v>464</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10933,16 +10969,18 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>502</v>
+        <v>196</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>503</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10990,7 +11028,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11011,21 +11049,21 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11036,7 +11074,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -11048,19 +11086,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>169</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>473</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>474</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>511</v>
+        <v>475</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>512</v>
+        <v>476</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -11085,13 +11123,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>21</v>
+        <v>478</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -11109,13 +11147,13 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
@@ -11130,21 +11168,21 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>514</v>
+        <v>464</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>21</v>
+        <v>480</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11167,13 +11205,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>508</v>
+        <v>196</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>517</v>
+        <v>483</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11224,7 +11262,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>518</v>
+        <v>484</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11245,21 +11283,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>514</v>
+        <v>464</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>21</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11282,19 +11320,19 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>521</v>
+        <v>487</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11343,7 +11381,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11364,7 +11402,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -11375,10 +11413,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11398,23 +11436,19 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>520</v>
+        <v>196</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>528</v>
+        <v>197</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -11462,7 +11496,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>199</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11474,7 +11508,7 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -11483,7 +11517,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>526</v>
+        <v>200</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -11494,21 +11528,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -11517,18 +11551,20 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>532</v>
+        <v>137</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11553,43 +11589,43 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>534</v>
+        <v>21</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>535</v>
+        <v>21</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>206</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -11598,7 +11634,7 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>537</v>
+        <v>200</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -11609,48 +11645,50 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>495</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>508</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>539</v>
+        <v>455</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q76" t="s" s="2">
-        <v>541</v>
-      </c>
+      <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11694,19 +11732,19 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
@@ -11715,7 +11753,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>526</v>
+        <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11726,10 +11764,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>543</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>543</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11740,7 +11778,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -11752,16 +11790,18 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>508</v>
+        <v>344</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>545</v>
+        <v>498</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11809,13 +11849,13 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
@@ -11830,7 +11870,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11841,10 +11881,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>547</v>
+        <v>502</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>547</v>
+        <v>502</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11867,16 +11907,18 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>548</v>
+        <v>504</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>549</v>
+        <v>505</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11924,7 +11966,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>550</v>
+        <v>507</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11936,7 +11978,7 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>508</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
@@ -11945,7 +11987,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11956,10 +11998,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>551</v>
+        <v>510</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>551</v>
+        <v>510</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11979,16 +12021,16 @@
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>520</v>
+        <v>196</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>552</v>
+        <v>197</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>553</v>
+        <v>198</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12039,7 +12081,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>554</v>
+        <v>199</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12051,7 +12093,7 @@
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -12060,7 +12102,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>526</v>
+        <v>200</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -12071,21 +12113,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -12094,18 +12136,20 @@
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>556</v>
+        <v>137</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -12130,43 +12174,43 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>534</v>
+        <v>21</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>535</v>
+        <v>21</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>558</v>
+        <v>206</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>21</v>
@@ -12175,7 +12219,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>537</v>
+        <v>200</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -12186,10 +12230,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>559</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>559</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12200,7 +12244,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
@@ -12212,17 +12256,15 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>110</v>
+        <v>513</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>560</v>
+        <v>514</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -12247,11 +12289,13 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>563</v>
+        <v>21</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>21</v>
@@ -12269,13 +12313,13 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>564</v>
+        <v>516</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
@@ -12290,7 +12334,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>200</v>
+        <v>517</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12301,10 +12345,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12315,7 +12359,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -12327,18 +12371,20 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>566</v>
+        <v>519</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>568</v>
+        <v>521</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -12386,13 +12432,13 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>570</v>
+        <v>524</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
@@ -12407,7 +12453,7 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>200</v>
+        <v>525</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -12418,10 +12464,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>571</v>
+        <v>526</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>571</v>
+        <v>526</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12432,7 +12478,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12444,20 +12490,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>110</v>
+        <v>519</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>572</v>
+        <v>527</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -12481,11 +12523,13 @@
         <v>21</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -12503,13 +12547,13 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>577</v>
+        <v>529</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
@@ -12524,7 +12568,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>578</v>
+        <v>525</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12535,10 +12579,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12561,16 +12605,20 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>581</v>
+        <v>532</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12618,7 +12666,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>583</v>
+        <v>536</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12639,7 +12687,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12650,10 +12698,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>585</v>
+        <v>538</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>585</v>
+        <v>538</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12676,18 +12724,20 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>169</v>
+        <v>531</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>586</v>
+        <v>539</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>587</v>
+        <v>540</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12711,13 +12761,13 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>589</v>
+        <v>21</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>590</v>
+        <v>21</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -12735,7 +12785,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12756,7 +12806,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>592</v>
+        <v>537</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12767,10 +12817,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>593</v>
+        <v>542</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>593</v>
+        <v>542</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12793,17 +12843,15 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>594</v>
+        <v>110</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>595</v>
+        <v>543</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -12828,13 +12876,13 @@
         <v>21</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>598</v>
+        <v>545</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>599</v>
+        <v>546</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>21</v>
@@ -12852,7 +12900,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>600</v>
+        <v>547</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12873,21 +12921,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>601</v>
+        <v>548</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>602</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>603</v>
+        <v>549</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>603</v>
+        <v>549</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12910,24 +12958,22 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>169</v>
+        <v>519</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="R87" t="s" s="2">
         <v>21</v>
       </c>
@@ -12947,13 +12993,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>608</v>
+        <v>21</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>609</v>
+        <v>21</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -12971,7 +13017,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>610</v>
+        <v>553</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12992,21 +13038,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>611</v>
+        <v>537</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>612</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>613</v>
+        <v>554</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>613</v>
+        <v>554</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13029,18 +13075,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>169</v>
+        <v>519</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>614</v>
+        <v>555</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>615</v>
+        <v>556</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>616</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -13064,13 +13108,13 @@
         <v>21</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>617</v>
+        <v>21</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>618</v>
+        <v>21</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -13088,7 +13132,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>619</v>
+        <v>557</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13109,21 +13153,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>620</v>
+        <v>537</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>621</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>622</v>
+        <v>558</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>622</v>
+        <v>558</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13146,20 +13190,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>169</v>
+        <v>531</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>623</v>
+        <v>559</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -13183,13 +13223,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>627</v>
+        <v>21</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>628</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -13207,7 +13247,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>629</v>
+        <v>561</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13228,21 +13268,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>630</v>
+        <v>537</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>631</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13253,7 +13293,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>21</v>
@@ -13265,13 +13305,13 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>633</v>
+        <v>563</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>634</v>
+        <v>564</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13322,13 +13362,13 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>635</v>
+        <v>565</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>21</v>
@@ -13343,21 +13383,21 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>21</v>
+        <v>537</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>636</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>637</v>
+        <v>566</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>637</v>
+        <v>566</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13377,16 +13417,16 @@
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>197</v>
+        <v>567</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>198</v>
+        <v>568</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13413,13 +13453,13 @@
         <v>21</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>21</v>
+        <v>545</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>21</v>
+        <v>546</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -13437,7 +13477,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>199</v>
+        <v>569</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13449,7 +13489,7 @@
         <v>21</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>21</v>
@@ -13458,7 +13498,7 @@
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>200</v>
+        <v>548</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -13469,14 +13509,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>638</v>
+        <v>570</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>638</v>
+        <v>570</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13492,19 +13532,19 @@
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>137</v>
+        <v>571</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>202</v>
+        <v>572</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>139</v>
+        <v>573</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13530,31 +13570,29 @@
         <v>21</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>21</v>
+        <v>574</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>206</v>
+        <v>575</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13566,7 +13604,7 @@
         <v>21</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>21</v>
@@ -13586,10 +13624,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>639</v>
+        <v>576</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>639</v>
+        <v>576</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13600,7 +13638,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -13612,18 +13650,18 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>169</v>
+        <v>577</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -13647,13 +13685,13 @@
         <v>21</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>643</v>
+        <v>21</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>644</v>
+        <v>21</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -13671,13 +13709,13 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>645</v>
+        <v>581</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
@@ -13692,21 +13730,21 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>646</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>647</v>
+        <v>582</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>647</v>
+        <v>582</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13717,7 +13755,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>21</v>
@@ -13729,19 +13767,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>648</v>
+        <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>649</v>
+        <v>583</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>650</v>
+        <v>584</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>651</v>
+        <v>585</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>652</v>
+        <v>586</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -13766,13 +13804,11 @@
         <v>21</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>21</v>
+        <v>587</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>21</v>
@@ -13790,13 +13826,13 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>653</v>
+        <v>588</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>21</v>
@@ -13811,21 +13847,21 @@
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>630</v>
+        <v>589</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>654</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13836,7 +13872,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13848,20 +13884,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>656</v>
+        <v>591</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>657</v>
+        <v>592</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>660</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -13909,7 +13941,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>661</v>
+        <v>594</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13930,21 +13962,21 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>662</v>
+        <v>595</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>663</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>664</v>
+        <v>596</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>664</v>
+        <v>596</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13967,20 +13999,18 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>665</v>
+        <v>169</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>666</v>
+        <v>597</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>667</v>
+        <v>598</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>669</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -14004,13 +14034,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>21</v>
+        <v>600</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>21</v>
+        <v>601</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -14028,7 +14058,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>670</v>
+        <v>602</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14049,21 +14079,21 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>671</v>
+        <v>603</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>672</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>673</v>
+        <v>604</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>673</v>
+        <v>604</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14086,20 +14116,18 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>674</v>
+        <v>605</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>675</v>
+        <v>606</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>676</v>
+        <v>607</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>678</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
@@ -14123,13 +14151,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>21</v>
+        <v>609</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>21</v>
+        <v>610</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -14147,7 +14175,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>679</v>
+        <v>611</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14168,21 +14196,21 @@
         <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>680</v>
+        <v>612</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>21</v>
+        <v>613</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>681</v>
+        <v>614</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>681</v>
+        <v>614</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14205,17 +14233,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>674</v>
+        <v>169</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>682</v>
+        <v>615</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="O98" t="s" s="2">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -14240,13 +14270,13 @@
         <v>21</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>21</v>
+        <v>620</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -14264,7 +14294,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>685</v>
+        <v>621</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14285,21 +14315,21 @@
         <v>21</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>680</v>
+        <v>622</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>21</v>
+        <v>623</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>686</v>
+        <v>624</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>624</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14319,19 +14349,21 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>687</v>
+        <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>688</v>
+        <v>625</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>689</v>
+        <v>626</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
       </c>
@@ -14355,13 +14387,13 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>21</v>
+        <v>628</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>21</v>
+        <v>629</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -14379,7 +14411,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>686</v>
+        <v>630</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14397,24 +14429,24 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>690</v>
+        <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>691</v>
+        <v>631</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>21</v>
+        <v>632</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>692</v>
+        <v>633</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>692</v>
+        <v>633</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14434,19 +14466,23 @@
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>197</v>
+        <v>634</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
       </c>
@@ -14470,13 +14506,13 @@
         <v>21</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>21</v>
+        <v>638</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>21</v>
+        <v>639</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -14494,7 +14530,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>199</v>
+        <v>640</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14506,7 +14542,7 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>21</v>
@@ -14515,25 +14551,25 @@
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>200</v>
+        <v>641</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>21</v>
+        <v>642</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>643</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14549,20 +14585,18 @@
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>503</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>137</v>
+        <v>644</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14611,7 +14645,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>206</v>
+        <v>646</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14623,7 +14657,7 @@
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>21</v>
@@ -14632,57 +14666,53 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>21</v>
+        <v>647</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>694</v>
+        <v>648</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>694</v>
+        <v>648</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>444</v>
+        <v>197</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
@@ -14730,19 +14760,19 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>446</v>
+        <v>199</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>21</v>
@@ -14751,7 +14781,7 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
@@ -14762,21 +14792,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>695</v>
+        <v>649</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>695</v>
+        <v>649</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>21</v>
@@ -14788,16 +14818,16 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>687</v>
+        <v>136</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>696</v>
+        <v>137</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>697</v>
+        <v>202</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>698</v>
+        <v>139</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14835,31 +14865,31 @@
         <v>21</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>695</v>
+        <v>206</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>21</v>
@@ -14868,7 +14898,7 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>699</v>
+        <v>200</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
@@ -14879,10 +14909,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14902,19 +14932,21 @@
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>197</v>
+        <v>651</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>198</v>
+        <v>652</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
       </c>
@@ -14938,13 +14970,13 @@
         <v>21</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>21</v>
+        <v>654</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>21</v>
+        <v>655</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>21</v>
@@ -14962,7 +14994,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>199</v>
+        <v>656</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14974,7 +15006,7 @@
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>21</v>
@@ -14983,32 +15015,32 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>21</v>
+        <v>657</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>701</v>
+        <v>658</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>701</v>
+        <v>658</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -15017,21 +15049,23 @@
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>136</v>
+        <v>659</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>137</v>
+        <v>660</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>202</v>
+        <v>661</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
@@ -15079,19 +15113,19 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>206</v>
+        <v>664</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>21</v>
@@ -15100,56 +15134,56 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>200</v>
+        <v>641</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>21</v>
+        <v>665</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>702</v>
+        <v>666</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>702</v>
+        <v>666</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>136</v>
+        <v>667</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>444</v>
+        <v>668</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>445</v>
+        <v>669</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>139</v>
+        <v>670</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>145</v>
+        <v>671</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -15198,19 +15232,19 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>446</v>
+        <v>672</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>21</v>
@@ -15219,21 +15253,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>133</v>
+        <v>673</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>21</v>
+        <v>674</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>703</v>
+        <v>675</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>703</v>
+        <v>675</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15253,19 +15287,23 @@
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>704</v>
+        <v>677</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
       </c>
@@ -15313,7 +15351,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>703</v>
+        <v>681</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15334,21 +15372,21 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>21</v>
+        <v>683</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15368,19 +15406,23 @@
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>708</v>
+        <v>685</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>709</v>
+        <v>686</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>689</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -15428,7 +15470,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15449,7 +15491,7 @@
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>21</v>
@@ -15460,10 +15502,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15483,19 +15525,21 @@
         <v>21</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>708</v>
+        <v>685</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>713</v>
+        <v>693</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
       </c>
@@ -15543,7 +15587,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15564,7 +15608,7 @@
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
@@ -15575,10 +15619,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15601,20 +15645,16 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>720</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -15662,7 +15702,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15680,10 +15720,10 @@
         <v>21</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
@@ -15694,10 +15734,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15720,17 +15760,15 @@
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>580</v>
+        <v>196</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>724</v>
+        <v>197</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
@@ -15779,7 +15817,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>723</v>
+        <v>199</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15791,41 +15829,41 @@
         <v>21</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>727</v>
+        <v>21</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>728</v>
+        <v>200</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>729</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>730</v>
+        <v>704</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>730</v>
+        <v>704</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>21</v>
@@ -15837,15 +15875,17 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>674</v>
+        <v>136</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>731</v>
+        <v>137</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>21</v>
@@ -15894,76 +15934,78 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>730</v>
+        <v>206</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>733</v>
+        <v>21</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>734</v>
+        <v>200</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>735</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>708</v>
+        <v>136</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>737</v>
+        <v>455</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>738</v>
+        <v>456</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
       </c>
@@ -16011,28 +16053,28 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>736</v>
+        <v>457</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>740</v>
+        <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>741</v>
+        <v>133</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -16043,10 +16085,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>742</v>
+        <v>706</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>742</v>
+        <v>706</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16069,15 +16111,17 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>743</v>
+        <v>698</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>744</v>
+        <v>707</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>709</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -16126,7 +16170,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>742</v>
+        <v>706</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16147,10 +16191,10 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>746</v>
+        <v>710</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>21</v>
@@ -16158,10 +16202,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>747</v>
+        <v>711</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>747</v>
+        <v>711</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16184,13 +16228,13 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>687</v>
+        <v>196</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>748</v>
+        <v>197</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>749</v>
+        <v>198</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16241,7 +16285,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>747</v>
+        <v>199</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16253,16 +16297,16 @@
         <v>21</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>750</v>
+        <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>751</v>
+        <v>200</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16273,21 +16317,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>752</v>
+        <v>712</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>752</v>
+        <v>712</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
@@ -16299,15 +16343,17 @@
         <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16356,19 +16402,19 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>21</v>
@@ -16388,14 +16434,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>753</v>
+        <v>713</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>753</v>
+        <v>713</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>135</v>
+        <v>454</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16408,24 +16454,26 @@
         <v>21</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>137</v>
+        <v>455</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>202</v>
+        <v>456</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
       </c>
@@ -16473,7 +16521,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>206</v>
+        <v>457</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16494,7 +16542,7 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16505,46 +16553,42 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>136</v>
+        <v>685</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>444</v>
+        <v>715</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>21</v>
       </c>
@@ -16592,19 +16636,19 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>446</v>
+        <v>714</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>21</v>
@@ -16613,7 +16657,7 @@
         <v>21</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>133</v>
+        <v>717</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>21</v>
@@ -16624,10 +16668,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>755</v>
+        <v>718</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>755</v>
+        <v>718</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16635,7 +16679,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>90</v>
@@ -16650,17 +16694,15 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>594</v>
+        <v>719</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>756</v>
+        <v>720</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>758</v>
-      </c>
+        <v>721</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16685,13 +16727,13 @@
         <v>21</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>759</v>
+        <v>21</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>760</v>
+        <v>21</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>21</v>
@@ -16709,10 +16751,10 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>755</v>
+        <v>718</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>90</v>
@@ -16727,24 +16769,24 @@
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>750</v>
+        <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>761</v>
+        <v>722</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>762</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16767,13 +16809,13 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>169</v>
+        <v>719</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>765</v>
+        <v>725</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16800,13 +16842,13 @@
         <v>21</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>766</v>
+        <v>21</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>767</v>
+        <v>21</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>21</v>
@@ -16824,7 +16866,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16842,24 +16884,24 @@
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>768</v>
+        <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>769</v>
+        <v>722</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>770</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>771</v>
+        <v>726</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>771</v>
+        <v>726</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16882,16 +16924,20 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>772</v>
+        <v>727</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>773</v>
+        <v>728</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>21</v>
       </c>
@@ -16939,7 +16985,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>771</v>
+        <v>726</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16954,13 +17000,13 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>775</v>
+        <v>21</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>768</v>
+        <v>732</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>776</v>
+        <v>733</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
@@ -16971,21 +17017,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>777</v>
+        <v>734</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>777</v>
+        <v>734</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>778</v>
+        <v>21</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>21</v>
@@ -16997,16 +17043,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>779</v>
+        <v>591</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>780</v>
+        <v>735</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>781</v>
+        <v>736</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>782</v>
+        <v>737</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17056,13 +17102,13 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>777</v>
+        <v>734</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>21</v>
@@ -17074,24 +17120,24 @@
         <v>21</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>21</v>
+        <v>738</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>783</v>
+        <v>739</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>21</v>
+        <v>740</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>784</v>
+        <v>741</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>784</v>
+        <v>741</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17102,7 +17148,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>21</v>
@@ -17114,17 +17160,15 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>785</v>
+        <v>685</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>786</v>
+        <v>742</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>788</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17173,13 +17217,13 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>784</v>
+        <v>741</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>21</v>
@@ -17188,23 +17232,1302 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
         <v>789</v>
       </c>
-      <c r="AL123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM123" t="s" s="2">
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K133" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="AN123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO123" t="s" s="2">
+      <c r="L133" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO123">
+  <autoFilter ref="A1:AO134">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17214,7 +18537,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
